--- a/data/trans_orig/P57_AC_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2007</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266503</t>
+          <t>268719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311345</t>
+          <t>311459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>264533</t>
+          <t>263252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>305329</t>
+          <t>305037</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>545814</t>
+          <t>544915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>606811</t>
+          <t>606464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182719</t>
+          <t>182605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>227561</t>
+          <t>225345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162160</t>
+          <t>162452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>202956</t>
+          <t>204237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>354742</t>
+          <t>355089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415739</t>
+          <t>416638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>435211</t>
+          <t>435611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>492701</t>
+          <t>491134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>386704</t>
+          <t>388733</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>435691</t>
+          <t>435546</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>841209</t>
+          <t>840774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>910884</t>
+          <t>914430</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>242788</t>
+          <t>244355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>300278</t>
+          <t>299878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188652</t>
+          <t>188797</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237639</t>
+          <t>235610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>448948</t>
+          <t>445402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>518623</t>
+          <t>519058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>414701</t>
+          <t>415776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>460666</t>
+          <t>461706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>457084</t>
+          <t>454739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>503974</t>
+          <t>504406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>888810</t>
+          <t>887169</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>957866</t>
+          <t>953850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176917</t>
+          <t>175877</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222882</t>
+          <t>221807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184790</t>
+          <t>184358</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231680</t>
+          <t>234025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>368481</t>
+          <t>372497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>437537</t>
+          <t>439178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>344614</t>
+          <t>344104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>386910</t>
+          <t>388364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>339804</t>
+          <t>339312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381228</t>
+          <t>379782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>697793</t>
+          <t>695679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>756839</t>
+          <t>754729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130687</t>
+          <t>129233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172983</t>
+          <t>173493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>134414</t>
+          <t>135860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175838</t>
+          <t>176330</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276400</t>
+          <t>278510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335446</t>
+          <t>337560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253138</t>
+          <t>252684</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290116</t>
+          <t>288827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>292690</t>
+          <t>292424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>325620</t>
+          <t>327295</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>554535</t>
+          <t>557386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>604884</t>
+          <t>605140</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,53%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96594</t>
+          <t>97883</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133572</t>
+          <t>134026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78366</t>
+          <t>76691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>111562</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>185812</t>
+          <t>185556</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236161</t>
+          <t>233310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210256</t>
+          <t>212330</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>239696</t>
+          <t>238442</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>251959</t>
+          <t>250076</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>280653</t>
+          <t>279882</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>471449</t>
+          <t>470703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>511309</t>
+          <t>511791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52887</t>
+          <t>54141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82327</t>
+          <t>80253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62281</t>
+          <t>63052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90975</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124208</t>
+          <t>123726</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164068</t>
+          <t>164814</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154143</t>
+          <t>153728</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176646</t>
+          <t>177287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255312</t>
+          <t>256244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284557</t>
+          <t>285383</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417917</t>
+          <t>417623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>455984</t>
+          <t>456612</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,97%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55740</t>
+          <t>56155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49351</t>
+          <t>48525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78596</t>
+          <t>77664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87807</t>
+          <t>87179</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125874</t>
+          <t>126168</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2170969</t>
+          <t>2172811</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2275537</t>
+          <t>2281084</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2333250</t>
+          <t>2334164</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2435811</t>
+          <t>2444053</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4539778</t>
+          <t>4540249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4688116</t>
+          <t>4681898</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>998372</t>
+          <t>992825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1102940</t>
+          <t>1101098</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>941255</t>
+          <t>933013</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1043816</t>
+          <t>1042902</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1962859</t>
+          <t>1969077</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2111197</t>
+          <t>2110726</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2012</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2012 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>234164</t>
+          <t>236501</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>278348</t>
+          <t>277932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>246594</t>
+          <t>244825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286019</t>
+          <t>285884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>494194</t>
+          <t>494762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>556353</t>
+          <t>551435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171859</t>
+          <t>172275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>216043</t>
+          <t>213706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142248</t>
+          <t>142383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181673</t>
+          <t>183442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>322120</t>
+          <t>327038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>384279</t>
+          <t>383711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>403365</t>
+          <t>399950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>452665</t>
+          <t>454749</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>400972</t>
+          <t>401195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447723</t>
+          <t>448352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>820501</t>
+          <t>821465</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>889996</t>
+          <t>889522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229981</t>
+          <t>227897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>279281</t>
+          <t>282696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162532</t>
+          <t>161903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209283</t>
+          <t>209060</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402906</t>
+          <t>403380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>472401</t>
+          <t>471437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>438779</t>
+          <t>439258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>487000</t>
+          <t>489462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>502425</t>
+          <t>499663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>551388</t>
+          <t>548017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>953962</t>
+          <t>956902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1024451</t>
+          <t>1027499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>191036</t>
+          <t>188574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>239257</t>
+          <t>238778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155363</t>
+          <t>158734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204326</t>
+          <t>207088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>360336</t>
+          <t>357288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>430825</t>
+          <t>427885</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>396344</t>
+          <t>392848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>445498</t>
+          <t>441206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>459773</t>
+          <t>460624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>502530</t>
+          <t>503014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>869557</t>
+          <t>866784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935643</t>
+          <t>935001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165021</t>
+          <t>169313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214175</t>
+          <t>217671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112692</t>
+          <t>112208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155449</t>
+          <t>154598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290098</t>
+          <t>290740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>356184</t>
+          <t>358957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>250475</t>
+          <t>251355</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>292784</t>
+          <t>292916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>309041</t>
+          <t>309079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>346219</t>
+          <t>346172</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>572251</t>
+          <t>572970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>627447</t>
+          <t>627093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132383</t>
+          <t>132251</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174692</t>
+          <t>173812</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100542</t>
+          <t>100589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137720</t>
+          <t>137682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244480</t>
+          <t>244834</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299676</t>
+          <t>298957</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>207597</t>
+          <t>209430</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238618</t>
+          <t>241531</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>249801</t>
+          <t>249671</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>280972</t>
+          <t>282010</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>470783</t>
+          <t>468842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>513427</t>
+          <t>513876</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68182</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99203</t>
+          <t>97370</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67474</t>
+          <t>66436</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98645</t>
+          <t>98775</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>141818</t>
+          <t>141369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>184462</t>
+          <t>186403</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170685</t>
+          <t>169926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198715</t>
+          <t>198200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>277383</t>
+          <t>277863</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>311829</t>
+          <t>311774</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>456196</t>
+          <t>456684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>502307</t>
+          <t>500285</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46907</t>
+          <t>47422</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74937</t>
+          <t>75696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70702</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105148</t>
+          <t>104668</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>125846</t>
+          <t>127868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>171957</t>
+          <t>171469</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2195742</t>
+          <t>2198487</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2312300</t>
+          <t>2310203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2536064</t>
+          <t>2540611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2640140</t>
+          <t>2644727</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4767294</t>
+          <t>4763531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4924822</t>
+          <t>4918237</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1086697</t>
+          <t>1088794</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1203255</t>
+          <t>1200510</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>898092</t>
+          <t>893505</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1002168</t>
+          <t>997621</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2012407</t>
+          <t>2018992</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2169935</t>
+          <t>2173698</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2016</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>295745</t>
+          <t>293889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>330742</t>
+          <t>332504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>277874</t>
+          <t>276946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>310456</t>
+          <t>311015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>582773</t>
+          <t>580969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>636056</t>
+          <t>633418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88721</t>
+          <t>86959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123718</t>
+          <t>125574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84337</t>
+          <t>83778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116919</t>
+          <t>117847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178200</t>
+          <t>180838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231483</t>
+          <t>233287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>427742</t>
+          <t>426459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>469324</t>
+          <t>468271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>418965</t>
+          <t>419011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>457941</t>
+          <t>457773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>859832</t>
+          <t>857224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>914118</t>
+          <t>913028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112034</t>
+          <t>113087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153616</t>
+          <t>154899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102228</t>
+          <t>102396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141204</t>
+          <t>141158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>227409</t>
+          <t>228499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>281695</t>
+          <t>284303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>497797</t>
+          <t>497596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>542923</t>
+          <t>541386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>501235</t>
+          <t>501862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>542352</t>
+          <t>544211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1013872</t>
+          <t>1014520</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1074085</t>
+          <t>1076416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125308</t>
+          <t>126845</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170434</t>
+          <t>170635</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115197</t>
+          <t>113338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156314</t>
+          <t>155687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251695</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311908</t>
+          <t>311260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>498024</t>
+          <t>496128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>540498</t>
+          <t>537701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>520187</t>
+          <t>518549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>557248</t>
+          <t>558336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1030349</t>
+          <t>1028440</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1086559</t>
+          <t>1084222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101213</t>
+          <t>104010</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143687</t>
+          <t>145583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86050</t>
+          <t>84962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123111</t>
+          <t>124749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198450</t>
+          <t>200787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254660</t>
+          <t>256569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>369531</t>
+          <t>368989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>403803</t>
+          <t>405059</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>395677</t>
+          <t>393831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>429498</t>
+          <t>427357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>773894</t>
+          <t>774085</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>825083</t>
+          <t>824915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72977</t>
+          <t>71721</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107249</t>
+          <t>107791</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62799</t>
+          <t>64940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96620</t>
+          <t>98466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>144162</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195183</t>
+          <t>194992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>244938</t>
+          <t>244530</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>276163</t>
+          <t>274981</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>318022</t>
+          <t>318584</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>343680</t>
+          <t>342712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>572338</t>
+          <t>572586</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>612259</t>
+          <t>611477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57108</t>
+          <t>58290</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88333</t>
+          <t>88741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>31965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56655</t>
+          <t>56093</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95689</t>
+          <t>96471</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135610</t>
+          <t>135362</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>205185</t>
+          <t>204614</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>226554</t>
+          <t>225997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>333297</t>
+          <t>331871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>362936</t>
+          <t>362483</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>543133</t>
+          <t>545296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>581871</t>
+          <t>580973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29579</t>
+          <t>30136</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50948</t>
+          <t>51519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35962</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65601</t>
+          <t>67027</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73160</t>
+          <t>74058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>111898</t>
+          <t>109735</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2618813</t>
+          <t>2620694</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2715505</t>
+          <t>2717371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2847958</t>
+          <t>2844493</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2934358</t>
+          <t>2937690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5495187</t>
+          <t>5497943</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5628988</t>
+          <t>5625830</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>661443</t>
+          <t>659577</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>758135</t>
+          <t>756254</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>587322</t>
+          <t>583990</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>673722</t>
+          <t>677187</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1269641</t>
+          <t>1272799</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1403442</t>
+          <t>1400686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2023</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2023 (tasa de respuesta: 98,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138951</t>
+          <t>134056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>207197</t>
+          <t>205969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113557</t>
+          <t>113622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159390</t>
+          <t>162329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>265726</t>
+          <t>265750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>352148</t>
+          <t>351240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>188544</t>
+          <t>189772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>256790</t>
+          <t>261685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145742</t>
+          <t>142803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191575</t>
+          <t>191510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>348725</t>
+          <t>349633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435147</t>
+          <t>435123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>221755</t>
+          <t>221857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>274018</t>
+          <t>273316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158498</t>
+          <t>147736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>287021</t>
+          <t>285323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>362036</t>
+          <t>382952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>541285</t>
+          <t>539609</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148135</t>
+          <t>148837</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>200398</t>
+          <t>200296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221494</t>
+          <t>223192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350017</t>
+          <t>360779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389384</t>
+          <t>391060</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568633</t>
+          <t>547717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>297076</t>
+          <t>299488</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>346588</t>
+          <t>346863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>305613</t>
+          <t>304540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>342872</t>
+          <t>342544</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>616798</t>
+          <t>617852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>676756</t>
+          <t>678000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185702</t>
+          <t>185427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>235214</t>
+          <t>232802</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197974</t>
+          <t>198302</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>235233</t>
+          <t>236306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>396379</t>
+          <t>395135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>456337</t>
+          <t>455283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>174584</t>
+          <t>186558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>552264</t>
+          <t>554414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>361183</t>
+          <t>353312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>456808</t>
+          <t>457199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>490177</t>
+          <t>515930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>987132</t>
+          <t>988998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,45%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327857</t>
+          <t>325707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>705537</t>
+          <t>693563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246804</t>
+          <t>246413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>342429</t>
+          <t>350300</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>596601</t>
+          <t>594735</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1093556</t>
+          <t>1067803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>358974</t>
+          <t>356032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>400135</t>
+          <t>400491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>368740</t>
+          <t>369610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>400670</t>
+          <t>400874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>739583</t>
+          <t>741296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>790063</t>
+          <t>792280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158550</t>
+          <t>158194</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199711</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139862</t>
+          <t>139658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171792</t>
+          <t>170922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309154</t>
+          <t>306937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359634</t>
+          <t>357921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>224667</t>
+          <t>225463</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>254895</t>
+          <t>254021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>244551</t>
+          <t>244550</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>269876</t>
+          <t>270655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>478816</t>
+          <t>478590</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>516527</t>
+          <t>518778</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109063</t>
+          <t>109937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139291</t>
+          <t>138495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>122958</t>
+          <t>122179</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148283</t>
+          <t>148284</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>240265</t>
+          <t>238014</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>277976</t>
+          <t>278202</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182191</t>
+          <t>184059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>206898</t>
+          <t>207725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>297688</t>
+          <t>298255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>322653</t>
+          <t>323313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>487360</t>
+          <t>488255</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>523984</t>
+          <t>521794</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68585</t>
+          <t>67758</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93292</t>
+          <t>91424</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93753</t>
+          <t>93093</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118718</t>
+          <t>118151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>167905</t>
+          <t>170095</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>204529</t>
+          <t>203634</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1473323</t>
+          <t>1502962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2122379</t>
+          <t>2115993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1927645</t>
+          <t>1933782</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2155887</t>
+          <t>2152435</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3468951</t>
+          <t>3540564</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4218069</t>
+          <t>4221190</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1306052</t>
+          <t>1312438</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1955108</t>
+          <t>1925469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1251989</t>
+          <t>1255441</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1480231</t>
+          <t>1474094</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2618238</t>
+          <t>2615117</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3367356</t>
+          <t>3295743</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_AC_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>268719</t>
+          <t>269933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311459</t>
+          <t>311775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>263252</t>
+          <t>264530</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>305037</t>
+          <t>305970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>544915</t>
+          <t>546766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>606464</t>
+          <t>602719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182605</t>
+          <t>182289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225345</t>
+          <t>224131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162452</t>
+          <t>161519</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>204237</t>
+          <t>202959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>355089</t>
+          <t>358834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>416638</t>
+          <t>414787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>435611</t>
+          <t>438558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>491134</t>
+          <t>491056</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>388733</t>
+          <t>387170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>435546</t>
+          <t>434706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>840774</t>
+          <t>839473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>914430</t>
+          <t>912490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244355</t>
+          <t>244433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299878</t>
+          <t>296931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188797</t>
+          <t>189637</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235610</t>
+          <t>237173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>445402</t>
+          <t>447342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>519058</t>
+          <t>520359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>415776</t>
+          <t>411932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>461706</t>
+          <t>461309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>454739</t>
+          <t>459171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>504406</t>
+          <t>506588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>887169</t>
+          <t>886765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>953850</t>
+          <t>955291</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>175877</t>
+          <t>176274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>221807</t>
+          <t>225651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184358</t>
+          <t>182176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>234025</t>
+          <t>229593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372497</t>
+          <t>371056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>439178</t>
+          <t>439582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>343990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>388364</t>
+          <t>387239</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>339312</t>
+          <t>337594</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>379782</t>
+          <t>382003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>695679</t>
+          <t>696287</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>754729</t>
+          <t>756863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129233</t>
+          <t>130358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173493</t>
+          <t>173607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135860</t>
+          <t>133639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176330</t>
+          <t>178048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>278510</t>
+          <t>276376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337560</t>
+          <t>336952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>252684</t>
+          <t>253982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>288827</t>
+          <t>291354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>292424</t>
+          <t>290979</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>327295</t>
+          <t>324714</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>557386</t>
+          <t>557275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>605140</t>
+          <t>606323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,68%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97883</t>
+          <t>95356</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134026</t>
+          <t>132728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76691</t>
+          <t>79272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111562</t>
+          <t>113007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>185556</t>
+          <t>184373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233310</t>
+          <t>233421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>212330</t>
+          <t>213050</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238442</t>
+          <t>240356</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>250076</t>
+          <t>250594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>279882</t>
+          <t>280109</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>470703</t>
+          <t>469945</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>511791</t>
+          <t>511096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54141</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80253</t>
+          <t>79533</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63052</t>
+          <t>62825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92858</t>
+          <t>92340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123726</t>
+          <t>124421</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164814</t>
+          <t>165572</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153728</t>
+          <t>153595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>177287</t>
+          <t>177141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>256244</t>
+          <t>257179</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>285383</t>
+          <t>286461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417623</t>
+          <t>421880</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>456612</t>
+          <t>456971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32596</t>
+          <t>32742</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56155</t>
+          <t>56288</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48525</t>
+          <t>47447</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>77664</t>
+          <t>76729</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87179</t>
+          <t>86820</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126168</t>
+          <t>121911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2172811</t>
+          <t>2179290</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2281084</t>
+          <t>2280419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2334164</t>
+          <t>2336294</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2444053</t>
+          <t>2438619</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4540249</t>
+          <t>4532346</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4681898</t>
+          <t>4684354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>992825</t>
+          <t>993490</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1101098</t>
+          <t>1094619</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>933013</t>
+          <t>938447</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1042902</t>
+          <t>1040772</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1969077</t>
+          <t>1966621</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2110726</t>
+          <t>2118629</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>236501</t>
+          <t>236392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>277932</t>
+          <t>276819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>244825</t>
+          <t>247606</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285884</t>
+          <t>284860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>494762</t>
+          <t>495585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>551435</t>
+          <t>552133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172275</t>
+          <t>173388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213706</t>
+          <t>213815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142383</t>
+          <t>143407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183442</t>
+          <t>180661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327038</t>
+          <t>326340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>383711</t>
+          <t>382888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399950</t>
+          <t>402616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>454749</t>
+          <t>454059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>401195</t>
+          <t>400784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>448352</t>
+          <t>447251</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>821465</t>
+          <t>820896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>889522</t>
+          <t>886763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227897</t>
+          <t>228587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>282696</t>
+          <t>280030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161903</t>
+          <t>163004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209060</t>
+          <t>209471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>403380</t>
+          <t>406139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>471437</t>
+          <t>472006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>439258</t>
+          <t>439881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>489462</t>
+          <t>490891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>499663</t>
+          <t>501233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>548017</t>
+          <t>550166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>956902</t>
+          <t>959668</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1027499</t>
+          <t>1024636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188574</t>
+          <t>187145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>238778</t>
+          <t>238155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158734</t>
+          <t>156585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207088</t>
+          <t>205518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357288</t>
+          <t>360151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>427885</t>
+          <t>425119</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>392848</t>
+          <t>394441</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>441206</t>
+          <t>441808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>460624</t>
+          <t>461465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>503014</t>
+          <t>502746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>866784</t>
+          <t>864128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935001</t>
+          <t>930488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>168711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217671</t>
+          <t>216078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112208</t>
+          <t>112476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154598</t>
+          <t>153757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290740</t>
+          <t>295253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358957</t>
+          <t>361613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>251355</t>
+          <t>251538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>292916</t>
+          <t>294085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>309079</t>
+          <t>307507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>346172</t>
+          <t>347465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>572970</t>
+          <t>569305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>627093</t>
+          <t>626556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132251</t>
+          <t>131082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173812</t>
+          <t>173629</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100589</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137682</t>
+          <t>139254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244834</t>
+          <t>245371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>298957</t>
+          <t>302622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>209430</t>
+          <t>209601</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>241531</t>
+          <t>241389</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>249671</t>
+          <t>250636</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>282010</t>
+          <t>280943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>468842</t>
+          <t>469344</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>513876</t>
+          <t>514459</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>65411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97370</t>
+          <t>97199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66436</t>
+          <t>67503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98775</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>141369</t>
+          <t>140786</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>186403</t>
+          <t>185901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>169926</t>
+          <t>170744</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198200</t>
+          <t>198067</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>277863</t>
+          <t>275949</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>311774</t>
+          <t>309999</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>456684</t>
+          <t>456833</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>500285</t>
+          <t>501067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47422</t>
+          <t>47555</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75696</t>
+          <t>74878</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70757</t>
+          <t>72532</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104668</t>
+          <t>106582</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>127868</t>
+          <t>127086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>171469</t>
+          <t>171320</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2198487</t>
+          <t>2197132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2310203</t>
+          <t>2310843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2540611</t>
+          <t>2538399</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2644727</t>
+          <t>2645490</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4763531</t>
+          <t>4769576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4918237</t>
+          <t>4920842</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1088794</t>
+          <t>1088154</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1200510</t>
+          <t>1201865</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>893505</t>
+          <t>892742</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>997621</t>
+          <t>999833</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2018992</t>
+          <t>2016387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2173698</t>
+          <t>2167653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>293889</t>
+          <t>298022</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>332504</t>
+          <t>332351</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>276946</t>
+          <t>279134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>311015</t>
+          <t>311915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>580969</t>
+          <t>585268</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>633418</t>
+          <t>632109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86959</t>
+          <t>87112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125574</t>
+          <t>121441</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83778</t>
+          <t>82878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117847</t>
+          <t>115659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180838</t>
+          <t>182147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233287</t>
+          <t>228988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>426459</t>
+          <t>427256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>468271</t>
+          <t>469793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>419011</t>
+          <t>420258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>457773</t>
+          <t>456258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>857224</t>
+          <t>857570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>913028</t>
+          <t>913673</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113087</t>
+          <t>111565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154899</t>
+          <t>154102</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102396</t>
+          <t>103911</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141158</t>
+          <t>139911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228499</t>
+          <t>227854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284303</t>
+          <t>283957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>497596</t>
+          <t>499162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>541386</t>
+          <t>541712</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>501862</t>
+          <t>503253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>544211</t>
+          <t>543979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1014520</t>
+          <t>1014310</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1076416</t>
+          <t>1074712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126845</t>
+          <t>126519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170635</t>
+          <t>169069</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113338</t>
+          <t>113570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155687</t>
+          <t>154296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249364</t>
+          <t>251068</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311260</t>
+          <t>311470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>496128</t>
+          <t>497401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>537701</t>
+          <t>539092</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>518549</t>
+          <t>519315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>558336</t>
+          <t>555601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1028440</t>
+          <t>1028470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1084222</t>
+          <t>1084103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104010</t>
+          <t>102619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145583</t>
+          <t>144310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84962</t>
+          <t>87697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124749</t>
+          <t>123983</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200787</t>
+          <t>200906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256569</t>
+          <t>256539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>368989</t>
+          <t>368953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>405059</t>
+          <t>403538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>393831</t>
+          <t>394385</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>427357</t>
+          <t>428439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>774085</t>
+          <t>775959</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>824915</t>
+          <t>824141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71721</t>
+          <t>73242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107791</t>
+          <t>107827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64940</t>
+          <t>63858</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98466</t>
+          <t>97912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144162</t>
+          <t>144936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194992</t>
+          <t>193118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>244530</t>
+          <t>243333</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>274981</t>
+          <t>275303</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>318584</t>
+          <t>319307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>342712</t>
+          <t>343338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>572586</t>
+          <t>573400</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>611477</t>
+          <t>611774</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58290</t>
+          <t>57968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88741</t>
+          <t>89938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56093</t>
+          <t>55370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>96174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135362</t>
+          <t>134548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204614</t>
+          <t>204861</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>225997</t>
+          <t>225660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>331871</t>
+          <t>330300</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>362483</t>
+          <t>361281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>545296</t>
+          <t>546556</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>580973</t>
+          <t>581890</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51519</t>
+          <t>51272</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>37617</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67027</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74058</t>
+          <t>73141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>109735</t>
+          <t>108475</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2620694</t>
+          <t>2625373</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2717371</t>
+          <t>2718147</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2844493</t>
+          <t>2848419</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2937690</t>
+          <t>2940170</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5497943</t>
+          <t>5492814</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5625830</t>
+          <t>5627169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>659577</t>
+          <t>658801</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>756254</t>
+          <t>751575</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>583990</t>
+          <t>581510</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>677187</t>
+          <t>673261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1272799</t>
+          <t>1271460</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1400686</t>
+          <t>1405815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>171835</t>
+          <t>184144</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134056</t>
+          <t>151165</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205969</t>
+          <t>217517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>136065</t>
+          <t>169050</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113622</t>
+          <t>143614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162329</t>
+          <t>195626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>307900</t>
+          <t>353195</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>265750</t>
+          <t>310265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>351240</t>
+          <t>391955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>223906</t>
+          <t>219143</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189772</t>
+          <t>185770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>261685</t>
+          <t>252122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>169067</t>
+          <t>185566</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142803</t>
+          <t>158990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191510</t>
+          <t>211002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>392973</t>
+          <t>404709</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>349633</t>
+          <t>365949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435123</t>
+          <t>447639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>395741</t>
+          <t>403287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>395741</t>
+          <t>403287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>395741</t>
+          <t>403287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>305132</t>
+          <t>354616</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>305132</t>
+          <t>354616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305132</t>
+          <t>354616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>700873</t>
+          <t>757904</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>700873</t>
+          <t>757904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>700873</t>
+          <t>757904</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>248854</t>
+          <t>287662</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>221857</t>
+          <t>259606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273316</t>
+          <t>316836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>239065</t>
+          <t>278875</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147736</t>
+          <t>254969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>285323</t>
+          <t>302332</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>487919</t>
+          <t>566537</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>382952</t>
+          <t>531318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>539609</t>
+          <t>607595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>173299</t>
+          <t>187758</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148837</t>
+          <t>158584</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>200296</t>
+          <t>215814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>269450</t>
+          <t>217464</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223192</t>
+          <t>194007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360779</t>
+          <t>241370</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>442750</t>
+          <t>405223</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391060</t>
+          <t>364165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>547717</t>
+          <t>440442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422153</t>
+          <t>475420</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422153</t>
+          <t>475420</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422153</t>
+          <t>475420</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>508515</t>
+          <t>496339</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>508515</t>
+          <t>496339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>508515</t>
+          <t>496339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>930669</t>
+          <t>971760</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>930669</t>
+          <t>971760</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>930669</t>
+          <t>971760</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>322647</t>
+          <t>384481</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299488</t>
+          <t>360344</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>346863</t>
+          <t>409597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>324041</t>
+          <t>382851</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>304540</t>
+          <t>363028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>342544</t>
+          <t>404368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>646687</t>
+          <t>767333</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>617852</t>
+          <t>735687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>678000</t>
+          <t>803018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>65,08%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>209643</t>
+          <t>229602</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185427</t>
+          <t>204486</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>232802</t>
+          <t>253739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>216805</t>
+          <t>237003</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198302</t>
+          <t>215486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>236306</t>
+          <t>256826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>426448</t>
+          <t>466605</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>395135</t>
+          <t>430920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>455283</t>
+          <t>498251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>532290</t>
+          <t>614083</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>532290</t>
+          <t>614083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>532290</t>
+          <t>614083</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>540846</t>
+          <t>619854</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>540846</t>
+          <t>619854</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>540846</t>
+          <t>619854</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1073135</t>
+          <t>1233938</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1073135</t>
+          <t>1233938</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1073135</t>
+          <t>1233938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>388934</t>
+          <t>427958</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186558</t>
+          <t>400308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>554414</t>
+          <t>455730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>428491</t>
+          <t>468337</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>353312</t>
+          <t>447181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>457199</t>
+          <t>488416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>817425</t>
+          <t>896294</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>515930</t>
+          <t>861784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>988998</t>
+          <t>929043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>491187</t>
+          <t>263543</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325707</t>
+          <t>235771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>693563</t>
+          <t>291193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>275121</t>
+          <t>259054</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246413</t>
+          <t>238975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350300</t>
+          <t>280210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>766308</t>
+          <t>522598</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594735</t>
+          <t>489849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1067803</t>
+          <t>557108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>880121</t>
+          <t>691501</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>880121</t>
+          <t>691501</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>880121</t>
+          <t>691501</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>703612</t>
+          <t>727391</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>703612</t>
+          <t>727391</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>703612</t>
+          <t>727391</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1583733</t>
+          <t>1418892</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1583733</t>
+          <t>1418892</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1583733</t>
+          <t>1418892</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>379593</t>
+          <t>416267</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>356032</t>
+          <t>393556</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>400491</t>
+          <t>437463</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>385679</t>
+          <t>431082</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>369610</t>
+          <t>413877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>400874</t>
+          <t>448052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>765272</t>
+          <t>847350</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>741296</t>
+          <t>817845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>792280</t>
+          <t>872988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>179092</t>
+          <t>190454</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158194</t>
+          <t>169258</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202653</t>
+          <t>213165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>154853</t>
+          <t>169177</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139658</t>
+          <t>152207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170922</t>
+          <t>186382</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>333945</t>
+          <t>359631</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306937</t>
+          <t>333993</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357921</t>
+          <t>389136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>558685</t>
+          <t>606721</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558685</t>
+          <t>606721</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558685</t>
+          <t>606721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>540532</t>
+          <t>600259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>540532</t>
+          <t>600259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>540532</t>
+          <t>600259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1099217</t>
+          <t>1206981</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1099217</t>
+          <t>1206981</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1099217</t>
+          <t>1206981</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>241177</t>
+          <t>267684</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>225463</t>
+          <t>251268</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>254021</t>
+          <t>282252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>257679</t>
+          <t>283330</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>244550</t>
+          <t>269944</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>270655</t>
+          <t>297885</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>498856</t>
+          <t>551014</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>478590</t>
+          <t>529318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>518778</t>
+          <t>571908</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>122781</t>
+          <t>135176</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109937</t>
+          <t>120608</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>138495</t>
+          <t>151592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>135155</t>
+          <t>145983</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>122179</t>
+          <t>131428</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148284</t>
+          <t>159369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>257936</t>
+          <t>281159</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238014</t>
+          <t>260265</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>278202</t>
+          <t>302855</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>363958</t>
+          <t>402860</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>363958</t>
+          <t>402860</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>363958</t>
+          <t>402860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>392834</t>
+          <t>429313</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>392834</t>
+          <t>429313</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>392834</t>
+          <t>429313</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>756792</t>
+          <t>832173</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>756792</t>
+          <t>832173</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>756792</t>
+          <t>832173</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>195576</t>
+          <t>215448</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>184059</t>
+          <t>201427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207725</t>
+          <t>228237</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>310208</t>
+          <t>338410</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>298255</t>
+          <t>323126</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>323313</t>
+          <t>351876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>505783</t>
+          <t>553858</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>488255</t>
+          <t>535767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>521794</t>
+          <t>573938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>79907</t>
+          <t>87035</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67758</t>
+          <t>74246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91424</t>
+          <t>101056</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>106198</t>
+          <t>116130</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93093</t>
+          <t>102664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118151</t>
+          <t>131414</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>186106</t>
+          <t>203166</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>170095</t>
+          <t>183086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>203634</t>
+          <t>221257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275483</t>
+          <t>302483</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275483</t>
+          <t>302483</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>275483</t>
+          <t>302483</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>416406</t>
+          <t>454540</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>416406</t>
+          <t>454540</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>416406</t>
+          <t>454540</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>691889</t>
+          <t>757024</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>691889</t>
+          <t>757024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>691889</t>
+          <t>757024</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1948615</t>
+          <t>2183645</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1502962</t>
+          <t>2119131</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2115993</t>
+          <t>2243836</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2081228</t>
+          <t>2351934</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1933782</t>
+          <t>2299379</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2152435</t>
+          <t>2411260</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4029843</t>
+          <t>4535579</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3540564</t>
+          <t>4453342</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4221190</t>
+          <t>4622930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1479816</t>
+          <t>1312712</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1312438</t>
+          <t>1252521</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1925469</t>
+          <t>1377226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1326648</t>
+          <t>1330379</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1255441</t>
+          <t>1271053</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1474094</t>
+          <t>1382934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2806464</t>
+          <t>2643091</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2615117</t>
+          <t>2555740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3295743</t>
+          <t>2725328</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3428431</t>
+          <t>3496357</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3428431</t>
+          <t>3496357</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3428431</t>
+          <t>3496357</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3407876</t>
+          <t>3682313</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3407876</t>
+          <t>3682313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3407876</t>
+          <t>3682313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6836307</t>
+          <t>7178670</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6836307</t>
+          <t>7178670</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6836307</t>
+          <t>7178670</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
